--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <color rgb="000070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
     </font>
     <font>
       <b val="1"/>
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -167,7 +171,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -536,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-08 ~ 2026-07-15  (최근 5거래일)  ·  캡처 3/7  ·  대기: TIME, TIME, PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-08 ~ 2026-07-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
         </is>
       </c>
     </row>
@@ -1054,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>804214400</v>
+        <v>433752000</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.59%</t>
+          <t>0.51%→0.61%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1098,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>433752000</v>
+        <v>804214400</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.61%</t>
+          <t>2.72%→2.59%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1163,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-455328000</v>
+        <v>-1512998400</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.44%</t>
+          <t>0.72%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -1207,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1512998400</v>
+        <v>-455328000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.47%</t>
+          <t>1.52%→1.44%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1274,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1386320000</v>
+        <v>1579760000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>3.89%→3.50%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1362,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1579760000</v>
+        <v>1386320000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>3.89%→3.50%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1427,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-931488000</v>
+        <v>-374380800</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.24%</t>
+          <t>1.04%→0.70%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>57→51</t>
         </is>
       </c>
     </row>
@@ -1455,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-376761600</v>
+        <v>-931488000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.17%</t>
+          <t>1.30%→1.24%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -1483,23 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-374380800</v>
+        <v>-376761600</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.70%</t>
+          <t>0.27%→0.17%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>57→51</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -1753,206 +1758,552 @@
       </c>
     </row>
     <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="n"/>
-      <c r="C35" s="19" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="19" t="n"/>
-      <c r="F35" s="19" t="n"/>
-      <c r="G35" s="19" t="n"/>
-      <c r="H35" s="19" t="n"/>
-      <c r="I35" s="19" t="n"/>
-      <c r="J35" s="19" t="n"/>
-      <c r="K35" s="19" t="n"/>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="n"/>
-      <c r="C37" s="19" t="n"/>
-      <c r="D37" s="19" t="n"/>
-      <c r="E37" s="19" t="n"/>
-      <c r="F37" s="19" t="n"/>
-      <c r="G37" s="19" t="n"/>
-      <c r="H37" s="19" t="n"/>
-      <c r="I37" s="19" t="n"/>
-      <c r="J37" s="19" t="n"/>
-      <c r="K37" s="19" t="n"/>
-    </row>
-    <row r="39" ht="19" customHeight="1">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 58억(2.2%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 6종목  /  매도 6종목</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="8" t="n"/>
+      <c r="J36" s="8" t="n"/>
+      <c r="K36" s="8" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>엘앤씨바이오  (신규)</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>6607510000</v>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.50%</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>0→140</t>
+        </is>
+      </c>
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>-470</v>
+      </c>
+      <c r="I38" s="15" t="n">
+        <v>-12926292500</v>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>9.07%→3.12%</t>
+        </is>
+      </c>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>770→300</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>89</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>6992685500</v>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>1.35%→4.46%</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>61→150</t>
+        </is>
+      </c>
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>-81</v>
+      </c>
+      <c r="I39" s="15" t="n">
+        <v>-4089244500</v>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>3.14%→1.32%</t>
+        </is>
+      </c>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>150→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>주성엔지니어링</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>6464619000</v>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>4.51%→7.48%</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>101→150</t>
+        </is>
+      </c>
+      <c r="G40" s="14" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>-51</v>
+      </c>
+      <c r="I40" s="15" t="n">
+        <v>-4440238500</v>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>3.44%→2.27%</t>
+        </is>
+      </c>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>120→69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>1214573500</v>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>1.45%→1.59%</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>42→59</t>
+        </is>
+      </c>
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I41" s="15" t="n">
+        <v>-2251252500</v>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>2.85%→2.39%</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>80→59</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B42" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>1191900000</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr">
+        <is>
+          <t>6.63%→10.59%</t>
+        </is>
+      </c>
+      <c r="E42" s="13" t="inlineStr">
+        <is>
+          <t>180→188</t>
+        </is>
+      </c>
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H42" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I42" s="15" t="n">
+        <v>-3637692500</v>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>4.20%→2.17%</t>
+        </is>
+      </c>
+      <c r="K42" s="13" t="inlineStr">
+        <is>
+          <t>49→30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B43" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>1090862500</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr">
+        <is>
+          <t>2.60%→2.89%</t>
+        </is>
+      </c>
+      <c r="E43" s="13" t="inlineStr">
+        <is>
+          <t>30→35</t>
+        </is>
+      </c>
+      <c r="G43" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I43" s="15" t="n">
+        <v>-235811250</v>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>1.89%→1.89%</t>
+        </is>
+      </c>
+      <c r="K43" s="13" t="inlineStr">
+        <is>
+          <t>200→191</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="19" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 50억(2.1%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B39" s="19" t="n"/>
-      <c r="C39" s="19" t="n"/>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="19" t="n"/>
-      <c r="F39" s="19" t="n"/>
-      <c r="G39" s="19" t="n"/>
-      <c r="H39" s="19" t="n"/>
-      <c r="I39" s="19" t="n"/>
-      <c r="J39" s="19" t="n"/>
-      <c r="K39" s="19" t="n"/>
-    </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="20" t="n"/>
+      <c r="D48" s="20" t="n"/>
+      <c r="E48" s="20" t="n"/>
+      <c r="F48" s="20" t="n"/>
+      <c r="G48" s="20" t="n"/>
+      <c r="H48" s="20" t="n"/>
+      <c r="I48" s="20" t="n"/>
+      <c r="J48" s="20" t="n"/>
+      <c r="K48" s="20" t="n"/>
+    </row>
+    <row r="50" ht="19" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 18억(3.4%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="8" t="n"/>
+      <c r="J51" s="8" t="n"/>
+      <c r="K51" s="8" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B43" s="9" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="G52" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H52" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J43" s="9" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="K52" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
         <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B44" s="11" t="n">
+      <c r="B53" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C44" s="11" t="n">
+      <c r="C53" s="11" t="n">
         <v>450162720</v>
       </c>
-      <c r="D44" s="12" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>1.61%→1.73%</t>
         </is>
       </c>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G44" s="17" t="n"/>
-      <c r="H44" s="17" t="n"/>
-      <c r="I44" s="17" t="n"/>
-      <c r="J44" s="17" t="n"/>
-      <c r="K44" s="17" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="G53" s="17" t="n"/>
+      <c r="H53" s="17" t="n"/>
+      <c r="I53" s="17" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B46" s="19" t="n"/>
-      <c r="C46" s="19" t="n"/>
-      <c r="D46" s="19" t="n"/>
-      <c r="E46" s="19" t="n"/>
-      <c r="F46" s="19" t="n"/>
-      <c r="G46" s="19" t="n"/>
-      <c r="H46" s="19" t="n"/>
-      <c r="I46" s="19" t="n"/>
-      <c r="J46" s="19" t="n"/>
-      <c r="K46" s="19" t="n"/>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20" t="n"/>
+      <c r="I55" s="20" t="n"/>
+      <c r="J55" s="20" t="n"/>
+      <c r="K55" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
     <mergeCell ref="A35:K35"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A39:K39"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="A55:K55"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A28:K28"/>
     <mergeCell ref="A46:K46"/>
+    <mergeCell ref="A36:E36"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A37:K37"/>
     <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,599억   ·   현금 211억(4.5%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 18종목  /  매도 21종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,585억   ·   현금 209억(4.5%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 18종목  /  매도 21종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>265</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>2397465600</v>
+        <v>2382964800</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-108</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1547043840</v>
+        <v>-1537686720</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>157</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2021557120</v>
+        <v>2009329960</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-74</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2767481600</v>
+        <v>-2750742800</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>97</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>6860771200</v>
+        <v>6819274600</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-45</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1312416000</v>
+        <v>-1304478000</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>43</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>517843840</v>
+        <v>514711720</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-476011200</v>
+        <v>-473132100</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>31</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2235670400</v>
+        <v>2222148200</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-32</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-6904320000</v>
+        <v>-6862560000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>24</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>861849600</v>
+        <v>856636800</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-30</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-807984000</v>
+        <v>-803097000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>21</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1491571200</v>
+        <v>1482549600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-29</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1303190400</v>
+        <v>-1295308200</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>20</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1027712000</v>
+        <v>1021496000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-22</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1665171200</v>
+        <v>-1655099600</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>13</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>459097600</v>
+        <v>456320800</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
         <v>-17</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-478937600</v>
+        <v>-476040800</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1059,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>433752000</v>
+        <v>799350200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.61%</t>
+          <t>2.72%→2.59%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1087,7 +1087,7 @@
         <v>-15</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-412920000</v>
+        <v>-410422500</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1103,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>804214400</v>
+        <v>431128500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.59%</t>
+          <t>0.51%→0.61%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1131,7 +1131,7 @@
         <v>-13</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-409448000</v>
+        <v>-406971500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1398720000</v>
+        <v>1390260000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1512998400</v>
+        <v>-452574000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.47%</t>
+          <t>1.52%→1.44%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>434000000</v>
+        <v>431375000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-455328000</v>
+        <v>-1503847200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.44%</t>
+          <t>0.72%→0.47%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -1242,7 +1242,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>857088000</v>
+        <v>851904000</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>-11</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-1918329600</v>
+        <v>-1906726800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1579760000</v>
+        <v>361369000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>2.67%→2.75%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1307,7 +1307,7 @@
         <v>-10</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-550560000</v>
+        <v>-547230000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>363568000</v>
+        <v>1377935000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.75%</t>
+          <t>3.89%→3.50%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1351,7 +1351,7 @@
         <v>-9</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-374529600</v>
+        <v>-372264300</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1367,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1386320000</v>
+        <v>1570205000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.89%→3.50%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1395,7 +1395,7 @@
         <v>-8</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1614976000</v>
+        <v>-1605208000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>3</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>310396800</v>
+        <v>308519400</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1432,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-374380800</v>
+        <v>-925854000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.70%</t>
+          <t>1.30%→1.24%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>57→51</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-931488000</v>
+        <v>-374482800</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.24%</t>
+          <t>0.27%→0.17%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-376761600</v>
+        <v>-372116400</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.17%</t>
+          <t>1.04%→0.70%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>57→51</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
         <v>-3</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-368131200</v>
+        <v>-365904600</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,227억   ·   현금 23억(0.6%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,024억   ·   현금 23억(0.6%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
         <v>83</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>452051200</v>
+        <v>448996800</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>-49</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-812224000</v>
+        <v>-806736000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>27</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1189209600</v>
+        <v>1181174400</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>-21</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-391608000</v>
+        <v>-388962000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
         <v>6</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>992784000</v>
+        <v>986076000</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1744,7 +1744,7 @@
         <v>-12</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-848217600</v>
+        <v>-842486400</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1760,7 +1760,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,673억   ·   현금 58억(2.2%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 6종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,662억   ·   현금 58억(2.2%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 6종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1856,7 +1856,7 @@
         <v>140</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>6607510000</v>
+        <v>6549634000</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>-470</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-12926292500</v>
+        <v>-12813069500</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>89</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>6992685500</v>
+        <v>6931435700</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>-81</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-4089244500</v>
+        <v>-4053426300</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>49</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>6464619000</v>
+        <v>6407994600</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>-51</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-4440238500</v>
+        <v>-4401345900</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>17</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1214573500</v>
+        <v>1203934900</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>-21</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-2251252500</v>
+        <v>-2231533500</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>1191900000</v>
+        <v>1181460000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>-19</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-3637692500</v>
+        <v>-3605829500</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>5</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>1090862500</v>
+        <v>1081307500</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>-9</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-235811250</v>
+        <v>-233745750</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,530억   ·   현금 50억(2.1%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,420억   ·   현금 50억(2.1%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2154,7 +2154,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 553억   ·   현금 18억(3.4%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 1종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 18억(3.4%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2250,7 +2250,7 @@
         <v>296</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>450162720</v>
+        <v>442596960</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>

--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -1059,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>799350200</v>
+        <v>431128500</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.59%</t>
+          <t>0.51%→0.61%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1103,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>431128500</v>
+        <v>799350200</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.61%</t>
+          <t>2.72%→2.59%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1168,23 +1168,23 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-452574000</v>
+        <v>-1503847200</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.44%</t>
+          <t>0.72%→0.47%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-1503847200</v>
+        <v>-452574000</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.47%</t>
+          <t>1.52%→1.44%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>361369000</v>
+        <v>1570205000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.75%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1377935000</v>
+        <v>361369000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.89%→3.50%</t>
+          <t>2.67%→2.75%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1367,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1570205000</v>
+        <v>1377935000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>3.89%→3.50%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1432,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-925854000</v>
+        <v>-374482800</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.24%</t>
+          <t>0.27%→0.17%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-374482800</v>
+        <v>-925854000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.17%</t>
+          <t>1.30%→1.24%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -1147,23 +1147,23 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1390260000</v>
+        <v>431375000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>3.57%→4.21%</t>
+          <t>1.82%→1.81%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>126→136</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>431375000</v>
+        <v>1390260000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.81%</t>
+          <t>3.57%→4.21%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>126→136</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1570205000</v>
+        <v>361369000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>2.67%→2.75%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>361369000</v>
+        <v>1570205000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.75%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1432,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-374482800</v>
+        <v>-372116400</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.17%</t>
+          <t>1.04%→0.70%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>57→51</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-925854000</v>
+        <v>-374482800</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.24%</t>
+          <t>0.27%→0.17%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-372116400</v>
+        <v>-925854000</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.70%</t>
+          <t>1.30%→1.24%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>57→51</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-07-08 ~ 2026-07-15  (최근 5거래일)  ·  캡처 5/7  ·  대기: PLUS, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-07-08 ~ 2026-07-15  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
@@ -1147,88 +1147,88 @@
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>431375000</v>
+        <v>1390260000</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>1.82%→1.81%</t>
+          <t>3.57%→4.21%</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>178→188</t>
+          <t>126→136</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H17" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1503847200</v>
+        <v>-452574000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>0.72%→0.47%</t>
+          <t>1.52%→1.44%</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>29→17</t>
+          <t>184→172</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1390260000</v>
+        <v>431375000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>3.57%→4.21%</t>
+          <t>1.82%→1.81%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>126→136</t>
+          <t>178→188</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H18" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-452574000</v>
+        <v>-1503847200</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>1.52%→1.44%</t>
+          <t>0.72%→0.47%</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>184→172</t>
+          <t>29→17</t>
         </is>
       </c>
     </row>
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1570205000</v>
+        <v>1377935000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>3.89%→3.50%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1367,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1377935000</v>
+        <v>1570205000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>3.89%→3.50%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1432,23 +1432,23 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>인텔리안테크</t>
         </is>
       </c>
       <c r="H23" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-372116400</v>
+        <v>-374482800</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.70%</t>
+          <t>0.27%→0.17%</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>57→51</t>
+          <t>18→12</t>
         </is>
       </c>
     </row>
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>인텔리안테크</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-374482800</v>
+        <v>-372116400</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.17%</t>
+          <t>1.04%→0.70%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>18→12</t>
+          <t>57→51</t>
         </is>
       </c>
     </row>
@@ -2135,176 +2135,886 @@
       </c>
     </row>
     <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="19" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B48" s="20" t="n"/>
-      <c r="C48" s="20" t="n"/>
-      <c r="D48" s="20" t="n"/>
-      <c r="E48" s="20" t="n"/>
-      <c r="F48" s="20" t="n"/>
-      <c r="G48" s="20" t="n"/>
-      <c r="H48" s="20" t="n"/>
-      <c r="I48" s="20" t="n"/>
-      <c r="J48" s="20" t="n"/>
-      <c r="K48" s="20" t="n"/>
-    </row>
-    <row r="50" ht="19" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 18억(3.4%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 1종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 341억   ·   현금 4억(100.0%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 10종목  /  매도 17종목</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="8" t="n"/>
+      <c r="J49" s="8" t="n"/>
+      <c r="K49" s="8" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="n"/>
-      <c r="C51" s="6" t="n"/>
-      <c r="D51" s="6" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>더블유씨피</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>209</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>145140050</v>
+      </c>
+      <c r="D51" s="12" t="inlineStr">
+        <is>
+          <t>6.16%→6.62%</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>3,020→3,229</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-174</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-40894350</v>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>0.42%→0.30%</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>601→427</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D52" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H52" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>101</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>323654500</v>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>5.92%→6.91%</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>629→730</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>서부T&amp;D</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-32527800</v>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>0.19%→0.10%</t>
+        </is>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>73→37</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>279845500</v>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>1.97%→2.80%</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>196→278</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>채비  (편출)</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-15028000</v>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>0.04%→0.00%</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>34→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>에프앤가이드</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>137772250</v>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>2.37%→2.79%</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>451→528</t>
+        </is>
+      </c>
+      <c r="G54" s="14" t="inlineStr">
+        <is>
+          <t>더핑크퐁컴퍼니</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I54" s="15" t="n">
+        <v>-29160100</v>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>0.21%→0.12%</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>82→48</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>알멕</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>36210000</v>
+      </c>
+      <c r="D55" s="12" t="inlineStr">
+        <is>
+          <t>0.59%→0.70%</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>83→98</t>
+        </is>
+      </c>
+      <c r="G55" s="14" t="inlineStr">
+        <is>
+          <t>액트로</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n">
+        <v>-29</v>
+      </c>
+      <c r="I55" s="15" t="n">
+        <v>-18832600</v>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>0.35%→0.30%</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>183→154</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>35700000</v>
+      </c>
+      <c r="D56" s="12" t="inlineStr">
+        <is>
+          <t>1.20%→1.31%</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>114→124</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>삼현  (편출)</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I56" s="15" t="n">
+        <v>-68964750</v>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.00%</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>코스메카코리아  (신규)</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>69785000</v>
+      </c>
+      <c r="D57" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.21%</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>0→10</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I57" s="15" t="n">
+        <v>-57693750</v>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>0.64%→0.48%</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>95→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>24097500</v>
+      </c>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>5.57%→5.67%</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>708→717</t>
+        </is>
+      </c>
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n">
+        <v>-25</v>
+      </c>
+      <c r="I58" s="15" t="n">
+        <v>-39142500</v>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>0.40%→0.29%</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>88→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>원익IPS</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>86428000</v>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>2.70%→2.97%</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>85→93</t>
+        </is>
+      </c>
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>브이엠</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I59" s="15" t="n">
+        <v>-224238500</v>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>4.81%→4.17%</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>168→145</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>36363000</v>
+      </c>
+      <c r="D60" s="12" t="inlineStr">
+        <is>
+          <t>0.87%→0.98%</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>49→55</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>오로스테크놀로지</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-22</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-33660000</v>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>0.38%→0.28%</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>85→63</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="17" t="n"/>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-18</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-332775000</v>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>4.78%→3.82%</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>88→70</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>하이록코리아</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-35700000</v>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.20%→0.10%</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>27→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>ISC</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-89250000</v>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>1.80%→1.54%</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>48→41</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="n"/>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-18615000</v>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>0.78%→0.72%</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>85→79</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="17" t="n"/>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="G65" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I65" s="15" t="n">
+        <v>-71910000</v>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>3.52%→3.33%</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>100→94</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="n"/>
+      <c r="B66" s="17" t="n"/>
+      <c r="C66" s="17" t="n"/>
+      <c r="D66" s="17" t="n"/>
+      <c r="E66" s="17" t="n"/>
+      <c r="G66" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I66" s="15" t="n">
+        <v>-79815000</v>
+      </c>
+      <c r="J66" s="16" t="inlineStr">
+        <is>
+          <t>1.64%→1.41%</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>42→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="n"/>
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="17" t="n"/>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="17" t="n"/>
+      <c r="G67" s="14" t="inlineStr">
+        <is>
+          <t>티씨케이</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I67" s="15" t="n">
+        <v>-60307500</v>
+      </c>
+      <c r="J67" s="16" t="inlineStr">
+        <is>
+          <t>2.78%→2.61%</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>47→44</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 517억   ·   현금 18억(3.4%)      오늘 2026-07-15  vs  5일전 2026-07-08      매수 1종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n"/>
+      <c r="E70" s="6" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="8" t="n"/>
+      <c r="J70" s="8" t="n"/>
+      <c r="K70" s="8" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H71" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
           <t>큐리오시스</t>
         </is>
       </c>
-      <c r="B53" s="11" t="n">
+      <c r="B72" s="11" t="n">
         <v>296</v>
       </c>
-      <c r="C53" s="11" t="n">
+      <c r="C72" s="11" t="n">
         <v>442596960</v>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>1.61%→1.73%</t>
         </is>
       </c>
-      <c r="E53" s="13" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>297→593</t>
         </is>
       </c>
-      <c r="G53" s="17" t="n"/>
-      <c r="H53" s="17" t="n"/>
-      <c r="I53" s="17" t="n"/>
-      <c r="J53" s="17" t="n"/>
-      <c r="K53" s="17" t="n"/>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="19" t="inlineStr">
+      <c r="G72" s="17" t="n"/>
+      <c r="H72" s="17" t="n"/>
+      <c r="I72" s="17" t="n"/>
+      <c r="J72" s="17" t="n"/>
+      <c r="K72" s="17" t="n"/>
+    </row>
+    <row r="74" ht="19" customHeight="1">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B55" s="20" t="n"/>
-      <c r="C55" s="20" t="n"/>
-      <c r="D55" s="20" t="n"/>
-      <c r="E55" s="20" t="n"/>
-      <c r="F55" s="20" t="n"/>
-      <c r="G55" s="20" t="n"/>
-      <c r="H55" s="20" t="n"/>
-      <c r="I55" s="20" t="n"/>
-      <c r="J55" s="20" t="n"/>
-      <c r="K55" s="20" t="n"/>
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="20" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="20" t="n"/>
+      <c r="J74" s="20" t="n"/>
+      <c r="K74" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="A48:K48"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G70:K70"/>
+    <mergeCell ref="A70:E70"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="A46:K46"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="A74:K74"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
     <mergeCell ref="A29:E29"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="G29:K29"/>
     <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A48:K48"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="G51:K51"/>
-    <mergeCell ref="A55:K55"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="G36:K36"/>
-    <mergeCell ref="A45:K45"/>
-    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A36:E36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260715.xlsx
+++ b/reports/pdf_rolling5_20260715.xlsx
@@ -1059,23 +1059,23 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>제주반도체</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>431128500</v>
+        <v>799350200</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>0.51%→0.61%</t>
+          <t>2.72%→2.59%</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>59→70</t>
+          <t>149→160</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1103,23 +1103,23 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>이엔에프테크놀로지</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>11</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>799350200</v>
+        <v>431128500</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>2.72%→2.59%</t>
+          <t>0.51%→0.61%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>149→160</t>
+          <t>59→70</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -1279,23 +1279,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>코미코</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>361369000</v>
+        <v>1570205000</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>2.67%→2.75%</t>
+          <t>2.95%→3.08%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>166→171</t>
+          <t>39→44</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1323,23 +1323,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>1377935000</v>
+        <v>361369000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>3.89%→3.50%</t>
+          <t>2.67%→2.75%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>52→57</t>
+          <t>166→171</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1367,23 +1367,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>1570205000</v>
+        <v>1377935000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.95%→3.08%</t>
+          <t>3.89%→3.50%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>39→44</t>
+          <t>52→57</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -1460,23 +1460,23 @@
       <c r="E24" s="17" t="n"/>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H24" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-372116400</v>
+        <v>-925854000</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>1.04%→0.70%</t>
+          <t>1.30%→1.24%</t>
         </is>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>57→51</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -1488,23 +1488,23 @@
       <c r="E25" s="17" t="n"/>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H25" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-925854000</v>
+        <v>-372116400</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>1.30%→1.24%</t>
+          <t>1.04%→0.70%</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>57→51</t>
         </is>
       </c>
     </row>
@@ -2335,23 +2335,23 @@
       </c>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>채비  (편출)</t>
+          <t>더핑크퐁컴퍼니</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-15028000</v>
+        <v>-29160100</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.04%→0.00%</t>
+          <t>0.21%→0.12%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>34→0</t>
+          <t>82→48</t>
         </is>
       </c>
     </row>
@@ -2379,23 +2379,23 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>더핑크퐁컴퍼니</t>
+          <t>채비  (편출)</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-34</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-29160100</v>
+        <v>-15028000</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.21%→0.12%</t>
+          <t>0.04%→0.00%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>82→48</t>
+          <t>34→0</t>
         </is>
       </c>
     </row>
@@ -2511,23 +2511,23 @@
       </c>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-57693750</v>
+        <v>-39142500</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.48%</t>
+          <t>0.40%→0.29%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>95→70</t>
+          <t>88→63</t>
         </is>
       </c>
     </row>
@@ -2555,23 +2555,23 @@
       </c>
       <c r="G58" s="14" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
         <v>-25</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-39142500</v>
+        <v>-57693750</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.40%→0.29%</t>
+          <t>0.64%→0.48%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>88→63</t>
+          <t>95→70</t>
         </is>
       </c>
     </row>
@@ -2755,23 +2755,23 @@
       <c r="E64" s="17" t="n"/>
       <c r="G64" s="14" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-18615000</v>
+        <v>-79815000</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>0.78%→0.72%</t>
+          <t>1.64%→1.41%</t>
         </is>
       </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>85→79</t>
+          <t>42→36</t>
         </is>
       </c>
     </row>
@@ -2811,23 +2811,23 @@
       <c r="E66" s="17" t="n"/>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="H66" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-79815000</v>
+        <v>-18615000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>1.64%→1.41%</t>
+          <t>0.78%→0.72%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>42→36</t>
+          <t>85→79</t>
         </is>
       </c>
     </row>
